--- a/server/templates/card_sales_daily_report.xlsx
+++ b/server/templates/card_sales_daily_report.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\ProjectCode\lavenmanager\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD6EFC1F-E17D-4A55-8F76-A5D17B38C23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA538DBA-F436-467D-9798-8D733A8978D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="41715" yWindow="750" windowWidth="25080" windowHeight="20250" xr2:uid="{2F9A52A0-41F6-4D58-9929-5793BF85A4AE}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{2F9A52A0-41F6-4D58-9929-5793BF85A4AE}"/>
   </bookViews>
   <sheets>
     <sheet name="A_카드 매출 일일 보고" sheetId="2" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'A_카드 매출 일일 보고'!$A$1:$J$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'A_카드 매출 일일 보고'!$A$1:$K$18</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -43,14 +43,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>A_카드 매출 일일 보고</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026.06.01</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>구매자</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -79,12 +71,20 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>입력자</t>
+    <t>담당</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드사</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>내   용 
-(점주계약금 / 독서지도사)</t>
+(점주보증금 / 독서지도사)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>A_카드 매출 일일 보고(교육사업부)</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -442,16 +442,16 @@
     <xf numFmtId="41" fontId="2" fillId="0" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -740,90 +740,94 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A1:K20"/>
   <sheetFormatPr defaultColWidth="8.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="2" customWidth="1"/>
-    <col min="4" max="4" width="16.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="11.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12.75" style="1" customWidth="1"/>
+    <col min="3" max="3" width="12.875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="20.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="23.75" style="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="25.875" style="2" customWidth="1"/>
-    <col min="9" max="9" width="16.5" style="2" customWidth="1"/>
-    <col min="10" max="10" width="24.25" style="1" customWidth="1"/>
-    <col min="11" max="12" width="8.625" style="1"/>
-    <col min="13" max="13" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="8.625" style="1"/>
+    <col min="7" max="7" width="12.625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="13.625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="21.625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="11.75" style="2" customWidth="1"/>
+    <col min="11" max="11" width="22" style="1" customWidth="1"/>
+    <col min="12" max="13" width="8.625" style="1"/>
+    <col min="14" max="14" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="42" customHeight="1">
-      <c r="A1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="22"/>
-      <c r="D1" s="22"/>
-      <c r="E1" s="22"/>
-      <c r="F1" s="22"/>
-      <c r="G1" s="22"/>
-      <c r="H1" s="22"/>
-      <c r="I1" s="22"/>
-      <c r="J1" s="22"/>
-    </row>
-    <row r="2" spans="1:10" ht="11.45" customHeight="1" thickBot="1"/>
-    <row r="3" spans="1:10" ht="45" customHeight="1">
+    <row r="1" spans="1:11" ht="42" customHeight="1">
+      <c r="A1" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+    </row>
+    <row r="2" spans="1:11" ht="11.45" customHeight="1" thickBot="1"/>
+    <row r="3" spans="1:11" ht="45" customHeight="1">
       <c r="A3" s="11" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B3" s="14" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C3" s="15" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="I3" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="17" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A4" s="23">
+      <c r="K3" s="18" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A4" s="22">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="s">
-        <v>2</v>
-      </c>
+      <c r="B4" s="13"/>
       <c r="C4" s="9"/>
       <c r="D4" s="10"/>
       <c r="E4" s="10"/>
       <c r="F4" s="12"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="20"/>
-      <c r="J4" s="8"/>
-    </row>
-    <row r="5" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A5" s="23">
+      <c r="I4" s="9"/>
+      <c r="J4" s="20"/>
+      <c r="K4" s="8"/>
+    </row>
+    <row r="5" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A5" s="22">
         <v>2</v>
       </c>
       <c r="B5" s="13"/>
@@ -833,11 +837,12 @@
       <c r="F5" s="12"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="8"/>
-    </row>
-    <row r="6" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A6" s="23">
+      <c r="I5" s="9"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="8"/>
+    </row>
+    <row r="6" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A6" s="22">
         <v>3</v>
       </c>
       <c r="B6" s="10"/>
@@ -847,11 +852,12 @@
       <c r="F6" s="12"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="8"/>
-    </row>
-    <row r="7" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A7" s="23">
+      <c r="I6" s="9"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="8"/>
+    </row>
+    <row r="7" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A7" s="22">
         <v>4</v>
       </c>
       <c r="B7" s="10"/>
@@ -861,11 +867,12 @@
       <c r="F7" s="12"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="I7" s="20"/>
-      <c r="J7" s="8"/>
-    </row>
-    <row r="8" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A8" s="23">
+      <c r="I7" s="9"/>
+      <c r="J7" s="20"/>
+      <c r="K7" s="8"/>
+    </row>
+    <row r="8" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A8" s="22">
         <v>5</v>
       </c>
       <c r="B8" s="10"/>
@@ -875,11 +882,12 @@
       <c r="F8" s="12"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="20"/>
-      <c r="J8" s="8"/>
-    </row>
-    <row r="9" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A9" s="23">
+      <c r="I8" s="9"/>
+      <c r="J8" s="20"/>
+      <c r="K8" s="8"/>
+    </row>
+    <row r="9" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A9" s="22">
         <v>6</v>
       </c>
       <c r="B9" s="10"/>
@@ -889,11 +897,12 @@
       <c r="F9" s="12"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="I9" s="20"/>
-      <c r="J9" s="8"/>
-    </row>
-    <row r="10" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A10" s="23">
+      <c r="I9" s="9"/>
+      <c r="J9" s="20"/>
+      <c r="K9" s="8"/>
+    </row>
+    <row r="10" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A10" s="22">
         <v>7</v>
       </c>
       <c r="B10" s="10"/>
@@ -903,11 +912,12 @@
       <c r="F10" s="12"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="8"/>
-    </row>
-    <row r="11" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A11" s="23">
+      <c r="I10" s="9"/>
+      <c r="J10" s="20"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A11" s="22">
         <v>8</v>
       </c>
       <c r="B11" s="10"/>
@@ -917,11 +927,12 @@
       <c r="F11" s="12"/>
       <c r="G11" s="9"/>
       <c r="H11" s="9"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="8"/>
-    </row>
-    <row r="12" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A12" s="23">
+      <c r="I11" s="9"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="8"/>
+    </row>
+    <row r="12" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A12" s="22">
         <v>9</v>
       </c>
       <c r="B12" s="10"/>
@@ -931,11 +942,12 @@
       <c r="F12" s="6"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="8"/>
-    </row>
-    <row r="13" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A13" s="23">
+      <c r="I12" s="9"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="8"/>
+    </row>
+    <row r="13" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A13" s="22">
         <v>10</v>
       </c>
       <c r="B13" s="10"/>
@@ -945,11 +957,12 @@
       <c r="F13" s="12"/>
       <c r="G13" s="9"/>
       <c r="H13" s="9"/>
-      <c r="I13" s="20"/>
-      <c r="J13" s="8"/>
-    </row>
-    <row r="14" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A14" s="23">
+      <c r="I13" s="9"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="8"/>
+    </row>
+    <row r="14" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A14" s="22">
         <v>11</v>
       </c>
       <c r="B14" s="3"/>
@@ -959,11 +972,12 @@
       <c r="F14" s="12"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="8"/>
-    </row>
-    <row r="15" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A15" s="23">
+      <c r="I14" s="9"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="8"/>
+    </row>
+    <row r="15" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A15" s="22">
         <v>12</v>
       </c>
       <c r="B15" s="3"/>
@@ -973,11 +987,12 @@
       <c r="F15" s="3"/>
       <c r="G15" s="9"/>
       <c r="H15" s="9"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="8"/>
-    </row>
-    <row r="16" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A16" s="23">
+      <c r="I15" s="9"/>
+      <c r="J15" s="20"/>
+      <c r="K15" s="8"/>
+    </row>
+    <row r="16" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A16" s="22">
         <v>13</v>
       </c>
       <c r="B16" s="3"/>
@@ -987,11 +1002,12 @@
       <c r="F16" s="3"/>
       <c r="G16" s="9"/>
       <c r="H16" s="9"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="8"/>
-    </row>
-    <row r="17" spans="1:10" ht="23.1" customHeight="1">
-      <c r="A17" s="23">
+      <c r="I16" s="9"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="8"/>
+    </row>
+    <row r="17" spans="1:11" ht="23.1" customHeight="1">
+      <c r="A17" s="22">
         <v>14</v>
       </c>
       <c r="B17" s="3"/>
@@ -1001,28 +1017,30 @@
       <c r="F17" s="3"/>
       <c r="G17" s="9"/>
       <c r="H17" s="9"/>
-      <c r="I17" s="20"/>
-      <c r="J17" s="8"/>
-    </row>
-    <row r="18" spans="1:10" ht="23.1" customHeight="1" thickBot="1">
-      <c r="A18" s="24">
+      <c r="I17" s="9"/>
+      <c r="J17" s="20"/>
+      <c r="K17" s="8"/>
+    </row>
+    <row r="18" spans="1:11" ht="23.1" customHeight="1" thickBot="1">
+      <c r="A18" s="23">
         <v>15</v>
       </c>
       <c r="B18" s="5"/>
       <c r="C18" s="7"/>
-      <c r="D18" s="25"/>
+      <c r="D18" s="24"/>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="21"/>
-      <c r="J18" s="4"/>
-    </row>
-    <row r="19" spans="1:10" ht="30" customHeight="1"/>
-    <row r="20" spans="1:10" ht="30" customHeight="1"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="21"/>
+      <c r="K18" s="4"/>
+    </row>
+    <row r="19" spans="1:11" ht="30" customHeight="1"/>
+    <row r="20" spans="1:11" ht="30" customHeight="1"/>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
